--- a/Models/Овцы и козы/results/Овцы и козы - Лучшие модели.xlsx
+++ b/Models/Овцы и козы/results/Овцы и козы - Лучшие модели.xlsx
@@ -462,17 +462,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>10.06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.86</v>
+        <v>10.12</v>
       </c>
       <c r="D2" t="n">
-        <v>8.17</v>
+        <v>10.47</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.63</v>
+        <v>4.04</v>
       </c>
       <c r="C3" t="n">
-        <v>8.289999999999999</v>
+        <v>4.41</v>
       </c>
       <c r="D3" t="n">
-        <v>11.57</v>
+        <v>9.52</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.43</v>
+        <v>11.6</v>
       </c>
       <c r="C4" t="n">
-        <v>13.86</v>
+        <v>10.21</v>
       </c>
       <c r="D4" t="n">
-        <v>24.06</v>
+        <v>18.38</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -525,17 +525,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.38</v>
+        <v>7.38</v>
       </c>
       <c r="C5" t="n">
-        <v>7.21</v>
+        <v>9.42</v>
       </c>
       <c r="D5" t="n">
-        <v>4.96</v>
+        <v>8.01</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.09</v>
+        <v>6.68</v>
       </c>
       <c r="C6" t="n">
-        <v>13.3</v>
+        <v>6.98</v>
       </c>
       <c r="D6" t="n">
-        <v>31.59</v>
+        <v>27.39</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1.938945707226866e+21</v>
+        <v>2.903022200075226e+21</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.22</v>
+        <v>14.25</v>
       </c>
       <c r="C8" t="n">
-        <v>9.390000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="D8" t="n">
-        <v>20.43</v>
+        <v>23.16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -605,17 +605,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.58</v>
+        <v>12.97</v>
       </c>
       <c r="C9" t="n">
-        <v>24.68</v>
+        <v>26.15</v>
       </c>
       <c r="D9" t="n">
-        <v>23.32</v>
+        <v>14.11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="C10" t="n">
-        <v>5.76</v>
+        <v>3.76</v>
       </c>
       <c r="D10" t="n">
-        <v>8.109999999999999</v>
+        <v>7.66</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="C11" t="n">
-        <v>3.97</v>
+        <v>3.39</v>
       </c>
       <c r="D11" t="n">
-        <v>6.58</v>
+        <v>7.22</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -668,17 +668,17 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7.37</v>
+        <v>6.52</v>
       </c>
       <c r="C12" t="n">
-        <v>8.52</v>
+        <v>6.11</v>
       </c>
       <c r="D12" t="n">
-        <v>22.82</v>
+        <v>13.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -689,17 +689,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20.26</v>
+        <v>16.97</v>
       </c>
       <c r="C13" t="n">
-        <v>18.93</v>
+        <v>15.16</v>
       </c>
       <c r="D13" t="n">
-        <v>17.37</v>
+        <v>16.37</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.8</v>
+        <v>17.16</v>
       </c>
       <c r="C14" t="n">
-        <v>14.49</v>
+        <v>16.42</v>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16.87</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.15</v>
+        <v>14.52</v>
       </c>
       <c r="C15" t="n">
-        <v>6.9</v>
+        <v>11.78</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9</v>
+        <v>16.19</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>30.5</v>
+        <v>9.91</v>
       </c>
       <c r="D16" t="n">
-        <v>38.76</v>
+        <v>22.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.97</v>
+        <v>5.67</v>
       </c>
       <c r="C17" t="n">
-        <v>63.65</v>
+        <v>6.13</v>
       </c>
       <c r="D17" t="n">
-        <v>69.48</v>
+        <v>17.17</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -794,17 +794,17 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12.2</v>
+        <v>13.37</v>
       </c>
       <c r="C18" t="n">
-        <v>31.37</v>
+        <v>3.3</v>
       </c>
       <c r="D18" t="n">
-        <v>64.90000000000001</v>
+        <v>106.59</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.48</v>
+        <v>2.58</v>
       </c>
       <c r="C19" t="n">
-        <v>6.04</v>
+        <v>6.07</v>
       </c>
       <c r="D19" t="n">
-        <v>10.05</v>
+        <v>8.24</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>8.279999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="D20" t="n">
-        <v>12.14</v>
+        <v>15.22</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,17 +857,17 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.16</v>
+        <v>8.41</v>
       </c>
       <c r="C21" t="n">
-        <v>14.9</v>
+        <v>12.21</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>11.24</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
